--- a/output/graficos_otras_relaciones/plot_comunal_d_otrasrel_a_2022_metropolitana.xlsx
+++ b/output/graficos_otras_relaciones/plot_comunal_d_otrasrel_a_2022_metropolitana.xlsx
@@ -398,22 +398,22 @@
         </is>
       </c>
       <c r="B2">
+        <v>17.62253260860031</v>
+      </c>
+      <c r="C2">
         <v>19.19061082830669</v>
-      </c>
-      <c r="C2">
-        <v>17.62253260860031</v>
       </c>
       <c r="D2">
         <v>5.210881555291465</v>
       </c>
       <c r="E2">
-        <v>14.02687661888031</v>
+        <v>12.88073072944717</v>
       </c>
       <c r="F2">
         <v>73.09239265167251</v>
       </c>
       <c r="G2">
-        <v>12.88073072944717</v>
+        <v>14.02687661888031</v>
       </c>
     </row>
     <row r="3">
@@ -423,22 +423,22 @@
         </is>
       </c>
       <c r="B3">
+        <v>27.86867041753035</v>
+      </c>
+      <c r="C3">
         <v>30.59113118152206</v>
-      </c>
-      <c r="C3">
-        <v>27.86867041753035</v>
       </c>
       <c r="D3">
         <v>3.268921289854195</v>
       </c>
       <c r="E3">
-        <v>19.30529438559198</v>
+        <v>17.58721779044371</v>
       </c>
       <c r="F3">
         <v>63.10748782396431</v>
       </c>
       <c r="G3">
-        <v>17.58721779044371</v>
+        <v>19.30529438559198</v>
       </c>
     </row>
     <row r="4">
@@ -448,22 +448,22 @@
         </is>
       </c>
       <c r="B4">
+        <v>27.93064413086605</v>
+      </c>
+      <c r="C4">
         <v>30.97925376312751</v>
-      </c>
-      <c r="C4">
-        <v>27.93064413086605</v>
       </c>
       <c r="D4">
         <v>3.227966714905933</v>
       </c>
       <c r="E4">
-        <v>19.49485474076216</v>
+        <v>17.57640304413144</v>
       </c>
       <c r="F4">
         <v>62.9287422151064</v>
       </c>
       <c r="G4">
-        <v>17.57640304413144</v>
+        <v>19.49485474076216</v>
       </c>
     </row>
     <row r="5">
@@ -473,22 +473,22 @@
         </is>
       </c>
       <c r="B5">
+        <v>26.92000049222894</v>
+      </c>
+      <c r="C5">
         <v>35.26328095197076</v>
-      </c>
-      <c r="C5">
-        <v>26.92000049222894</v>
       </c>
       <c r="D5">
         <v>2.835810999441652</v>
       </c>
       <c r="E5">
+        <v>16.59850525437232</v>
+      </c>
+      <c r="F5">
+        <v>61.65863651883607</v>
+      </c>
+      <c r="G5">
         <v>21.74285822679161</v>
-      </c>
-      <c r="F5">
-        <v>61.65863651883608</v>
-      </c>
-      <c r="G5">
-        <v>16.59850525437232</v>
       </c>
     </row>
     <row r="6">
@@ -498,22 +498,22 @@
         </is>
       </c>
       <c r="B6">
+        <v>29.34756679389313</v>
+      </c>
+      <c r="C6">
         <v>34.375993956743</v>
-      </c>
-      <c r="C6">
-        <v>29.34756679389313</v>
       </c>
       <c r="D6">
         <v>2.90900679485326</v>
       </c>
       <c r="E6">
-        <v>20.99636350390665</v>
+        <v>17.92507239601989</v>
       </c>
       <c r="F6">
         <v>61.07856410007346</v>
       </c>
       <c r="G6">
-        <v>17.92507239601989</v>
+        <v>20.99636350390665</v>
       </c>
     </row>
     <row r="7">
@@ -523,22 +523,22 @@
         </is>
       </c>
       <c r="B7">
+        <v>24.61887523581298</v>
+      </c>
+      <c r="C7">
         <v>24.9766311460086</v>
-      </c>
-      <c r="C7">
-        <v>24.61887523581298</v>
       </c>
       <c r="D7">
         <v>4.00374251497006</v>
       </c>
       <c r="E7">
-        <v>16.69611056515243</v>
+        <v>16.45696173050597</v>
       </c>
       <c r="F7">
-        <v>66.8469277043416</v>
+        <v>66.84692770434161</v>
       </c>
       <c r="G7">
-        <v>16.45696173050596</v>
+        <v>16.69611056515244</v>
       </c>
     </row>
     <row r="8">
@@ -548,22 +548,22 @@
         </is>
       </c>
       <c r="B8">
+        <v>29.8679222576569</v>
+      </c>
+      <c r="C8">
         <v>24.36518442746254</v>
-      </c>
-      <c r="C8">
-        <v>29.8679222576569</v>
       </c>
       <c r="D8">
         <v>4.104216830277212</v>
       </c>
       <c r="E8">
-        <v>15.79763576779027</v>
+        <v>19.36544163545568</v>
       </c>
       <c r="F8">
-        <v>64.83692259675406</v>
+        <v>64.83692259675405</v>
       </c>
       <c r="G8">
-        <v>19.36544163545569</v>
+        <v>15.79763576779026</v>
       </c>
     </row>
     <row r="9">
@@ -573,22 +573,22 @@
         </is>
       </c>
       <c r="B9">
+        <v>24.78816672380859</v>
+      </c>
+      <c r="C9">
         <v>23.87226330998677</v>
-      </c>
-      <c r="C9">
-        <v>24.78816672380859</v>
       </c>
       <c r="D9">
         <v>4.18896183832581</v>
       </c>
       <c r="E9">
-        <v>16.05824986821297</v>
+        <v>16.67435424354244</v>
       </c>
       <c r="F9">
         <v>67.26739588824459</v>
       </c>
       <c r="G9">
-        <v>16.67435424354244</v>
+        <v>16.05824986821297</v>
       </c>
     </row>
     <row r="10">
@@ -598,22 +598,22 @@
         </is>
       </c>
       <c r="B10">
+        <v>25.25105584232755</v>
+      </c>
+      <c r="C10">
         <v>33.09088065071172</v>
-      </c>
-      <c r="C10">
-        <v>25.25105584232755</v>
       </c>
       <c r="D10">
         <v>3.02198061923895</v>
       </c>
       <c r="E10">
-        <v>20.89836804046312</v>
+        <v>15.94716876753467</v>
       </c>
       <c r="F10">
         <v>63.15446319200221</v>
       </c>
       <c r="G10">
-        <v>15.94716876753467</v>
+        <v>20.89836804046312</v>
       </c>
     </row>
     <row r="11">
@@ -623,22 +623,22 @@
         </is>
       </c>
       <c r="B11">
+        <v>25.29460033330232</v>
+      </c>
+      <c r="C11">
         <v>35.23572256388999</v>
-      </c>
-      <c r="C11">
-        <v>25.29460033330232</v>
       </c>
       <c r="D11">
         <v>2.838028929836144</v>
       </c>
       <c r="E11">
-        <v>21.94957434082771</v>
+        <v>15.75689868231413</v>
       </c>
       <c r="F11">
         <v>62.29352697685815</v>
       </c>
       <c r="G11">
-        <v>15.75689868231413</v>
+        <v>21.94957434082771</v>
       </c>
     </row>
     <row r="12">
@@ -648,22 +648,22 @@
         </is>
       </c>
       <c r="B12">
+        <v>27.98899616735441</v>
+      </c>
+      <c r="C12">
         <v>36.55836438176889</v>
-      </c>
-      <c r="C12">
-        <v>27.98899616735441</v>
       </c>
       <c r="D12">
         <v>2.735352133255406</v>
       </c>
       <c r="E12">
-        <v>22.2175331526238</v>
+        <v>17.00969014267396</v>
       </c>
       <c r="F12">
         <v>60.77277670470224</v>
       </c>
       <c r="G12">
-        <v>17.00969014267396</v>
+        <v>22.2175331526238</v>
       </c>
     </row>
     <row r="13">
@@ -673,22 +673,22 @@
         </is>
       </c>
       <c r="B13">
+        <v>32.88624817620897</v>
+      </c>
+      <c r="C13">
         <v>28.11978132086417</v>
-      </c>
-      <c r="C13">
-        <v>32.88624817620897</v>
       </c>
       <c r="D13">
         <v>3.556215422123589</v>
       </c>
       <c r="E13">
-        <v>17.4650486125896</v>
+        <v>20.42547616318108</v>
       </c>
       <c r="F13">
         <v>62.10947522422932</v>
       </c>
       <c r="G13">
-        <v>20.42547616318108</v>
+        <v>17.4650486125896</v>
       </c>
     </row>
     <row r="14">
@@ -698,22 +698,22 @@
         </is>
       </c>
       <c r="B14">
+        <v>24.83464677737124</v>
+      </c>
+      <c r="C14">
         <v>39.33119898677174</v>
-      </c>
-      <c r="C14">
-        <v>24.83464677737124</v>
       </c>
       <c r="D14">
         <v>2.542510845744443</v>
       </c>
       <c r="E14">
-        <v>23.95821055451379</v>
+        <v>15.12777926600589</v>
       </c>
       <c r="F14">
         <v>60.91401017948031</v>
       </c>
       <c r="G14">
-        <v>15.12777926600589</v>
+        <v>23.95821055451379</v>
       </c>
     </row>
     <row r="15">
@@ -723,22 +723,22 @@
         </is>
       </c>
       <c r="B15">
+        <v>20.29366598649473</v>
+      </c>
+      <c r="C15">
         <v>38.22390979657951</v>
-      </c>
-      <c r="C15">
-        <v>20.29366598649473</v>
       </c>
       <c r="D15">
         <v>2.616163561817231</v>
       </c>
       <c r="E15">
-        <v>24.11335753007452</v>
+        <v>12.80215514667339</v>
       </c>
       <c r="F15">
         <v>63.0844873232521</v>
       </c>
       <c r="G15">
-        <v>12.80215514667339</v>
+        <v>24.11335753007452</v>
       </c>
     </row>
     <row r="16">
@@ -748,22 +748,22 @@
         </is>
       </c>
       <c r="B16">
+        <v>27.80680852249766</v>
+      </c>
+      <c r="C16">
         <v>24.33705391357664</v>
-      </c>
-      <c r="C16">
-        <v>27.80680852249766</v>
       </c>
       <c r="D16">
         <v>4.108960778700258</v>
       </c>
       <c r="E16">
-        <v>15.99607997582041</v>
+        <v>18.27665479058095</v>
       </c>
       <c r="F16">
         <v>65.72726523359864</v>
       </c>
       <c r="G16">
-        <v>18.27665479058095</v>
+        <v>15.99607997582041</v>
       </c>
     </row>
     <row r="17">
@@ -773,22 +773,22 @@
         </is>
       </c>
       <c r="B17">
+        <v>27.82187562858779</v>
+      </c>
+      <c r="C17">
         <v>33.46640053226879</v>
-      </c>
-      <c r="C17">
-        <v>27.82187562858779</v>
       </c>
       <c r="D17">
         <v>2.988071570576541</v>
       </c>
       <c r="E17">
+        <v>17.24978175155172</v>
+      </c>
+      <c r="F17">
+        <v>62.00078665374764</v>
+      </c>
+      <c r="G17">
         <v>20.74943159470064</v>
-      </c>
-      <c r="F17">
-        <v>62.00078665374765</v>
-      </c>
-      <c r="G17">
-        <v>17.24978175155173</v>
       </c>
     </row>
     <row r="18">
@@ -798,22 +798,22 @@
         </is>
       </c>
       <c r="B18">
+        <v>26.479802143446</v>
+      </c>
+      <c r="C18">
         <v>34.9002473206925</v>
-      </c>
-      <c r="C18">
-        <v>26.479802143446</v>
       </c>
       <c r="D18">
         <v>2.865309207729012</v>
       </c>
       <c r="E18">
-        <v>21.62612258242488</v>
+        <v>16.40834925467679</v>
       </c>
       <c r="F18">
         <v>61.96552816289833</v>
       </c>
       <c r="G18">
-        <v>16.40834925467679</v>
+        <v>21.62612258242488</v>
       </c>
     </row>
     <row r="19">
@@ -823,22 +823,22 @@
         </is>
       </c>
       <c r="B19">
+        <v>23.03469450414492</v>
+      </c>
+      <c r="C19">
         <v>35.11452256677924</v>
-      </c>
-      <c r="C19">
-        <v>23.03469450414492</v>
       </c>
       <c r="D19">
         <v>2.847824566312255</v>
       </c>
       <c r="E19">
+        <v>14.56516505789257</v>
+      </c>
+      <c r="F19">
+        <v>63.23142273613256</v>
+      </c>
+      <c r="G19">
         <v>22.20341220597485</v>
-      </c>
-      <c r="F19">
-        <v>63.23142273613258</v>
-      </c>
-      <c r="G19">
-        <v>14.56516505789257</v>
       </c>
     </row>
     <row r="20">
@@ -848,22 +848,22 @@
         </is>
       </c>
       <c r="B20">
+        <v>26.02166758091059</v>
+      </c>
+      <c r="C20">
         <v>31.94098139929187</v>
-      </c>
-      <c r="C20">
-        <v>26.02166758091059</v>
       </c>
       <c r="D20">
         <v>3.13077418473488</v>
       </c>
       <c r="E20">
-        <v>20.22059113689278</v>
+        <v>16.47330413164437</v>
       </c>
       <c r="F20">
         <v>63.30610473146285</v>
       </c>
       <c r="G20">
-        <v>16.47330413164437</v>
+        <v>20.22059113689278</v>
       </c>
     </row>
     <row r="21">
@@ -873,22 +873,22 @@
         </is>
       </c>
       <c r="B21">
+        <v>19.64715528870315</v>
+      </c>
+      <c r="C21">
         <v>32.53167402861904</v>
-      </c>
-      <c r="C21">
-        <v>19.64715528870315</v>
       </c>
       <c r="D21">
         <v>3.073927271988129</v>
       </c>
       <c r="E21">
+        <v>12.91057066008508</v>
+      </c>
+      <c r="F21">
+        <v>65.71216275522841</v>
+      </c>
+      <c r="G21">
         <v>21.37726658468651</v>
-      </c>
-      <c r="F21">
-        <v>65.71216275522842</v>
-      </c>
-      <c r="G21">
-        <v>12.91057066008508</v>
       </c>
     </row>
     <row r="22">
@@ -898,22 +898,22 @@
         </is>
       </c>
       <c r="B22">
+        <v>27.47361530232632</v>
+      </c>
+      <c r="C22">
         <v>41.59920805990644</v>
-      </c>
-      <c r="C22">
-        <v>27.47361530232632</v>
       </c>
       <c r="D22">
         <v>2.403891916788209</v>
       </c>
       <c r="E22">
-        <v>24.60431382918446</v>
+        <v>16.2495750387187</v>
       </c>
       <c r="F22">
         <v>59.14611113209686</v>
       </c>
       <c r="G22">
-        <v>16.2495750387187</v>
+        <v>24.60431382918446</v>
       </c>
     </row>
     <row r="23">
@@ -923,22 +923,22 @@
         </is>
       </c>
       <c r="B23">
+        <v>26.27897503786963</v>
+      </c>
+      <c r="C23">
         <v>28.4881426698405</v>
-      </c>
-      <c r="C23">
-        <v>26.27897503786963</v>
       </c>
       <c r="D23">
         <v>3.510232350312779</v>
       </c>
       <c r="E23">
-        <v>18.40710293748741</v>
+        <v>16.97968885580692</v>
       </c>
       <c r="F23">
         <v>64.61320820670568</v>
       </c>
       <c r="G23">
-        <v>16.97968885580692</v>
+        <v>18.40710293748741</v>
       </c>
     </row>
     <row r="24">
@@ -948,22 +948,22 @@
         </is>
       </c>
       <c r="B24">
+        <v>15.23000612838977</v>
+      </c>
+      <c r="C24">
         <v>32.45173893059599</v>
-      </c>
-      <c r="C24">
-        <v>15.23000612838977</v>
       </c>
       <c r="D24">
         <v>3.081498967246976</v>
       </c>
       <c r="E24">
-        <v>21.97410310775675</v>
+        <v>10.31272085951228</v>
       </c>
       <c r="F24">
         <v>67.71317603273098</v>
       </c>
       <c r="G24">
-        <v>10.31272085951228</v>
+        <v>21.97410310775675</v>
       </c>
     </row>
     <row r="25">
@@ -973,22 +973,22 @@
         </is>
       </c>
       <c r="B25">
+        <v>28.89824909150975</v>
+      </c>
+      <c r="C25">
         <v>27.55134346437617</v>
-      </c>
-      <c r="C25">
-        <v>28.89824909150975</v>
       </c>
       <c r="D25">
         <v>3.629587070020734</v>
       </c>
       <c r="E25">
-        <v>17.61036447220817</v>
+        <v>18.47128434111255</v>
       </c>
       <c r="F25">
         <v>63.91835118667928</v>
       </c>
       <c r="G25">
-        <v>18.47128434111255</v>
+        <v>17.61036447220817</v>
       </c>
     </row>
     <row r="26">
@@ -998,22 +998,22 @@
         </is>
       </c>
       <c r="B26">
+        <v>29.07711669366782</v>
+      </c>
+      <c r="C26">
         <v>19.36434873905758</v>
-      </c>
-      <c r="C26">
-        <v>29.07711669366782</v>
       </c>
       <c r="D26">
         <v>5.164129263913824</v>
       </c>
       <c r="E26">
-        <v>13.04510749918029</v>
+        <v>19.5882711134011</v>
       </c>
       <c r="F26">
         <v>67.36662138741862</v>
       </c>
       <c r="G26">
-        <v>19.5882711134011</v>
+        <v>13.04510749918029</v>
       </c>
     </row>
     <row r="27">
@@ -1023,22 +1023,22 @@
         </is>
       </c>
       <c r="B27">
+        <v>25.07290670275063</v>
+      </c>
+      <c r="C27">
         <v>29.86375195389963</v>
-      </c>
-      <c r="C27">
-        <v>25.07290670275063</v>
       </c>
       <c r="D27">
         <v>3.348541072614351</v>
       </c>
       <c r="E27">
-        <v>19.2748134707614</v>
+        <v>16.18268195541368</v>
       </c>
       <c r="F27">
         <v>64.54250457382493</v>
       </c>
       <c r="G27">
-        <v>16.18268195541368</v>
+        <v>19.2748134707614</v>
       </c>
     </row>
     <row r="28">
@@ -1048,22 +1048,22 @@
         </is>
       </c>
       <c r="B28">
+        <v>26.33227684823469</v>
+      </c>
+      <c r="C28">
         <v>30.88099800987691</v>
-      </c>
-      <c r="C28">
-        <v>26.33227684823469</v>
       </c>
       <c r="D28">
         <v>3.238237312408629</v>
       </c>
       <c r="E28">
+        <v>16.74939783043139</v>
+      </c>
+      <c r="F28">
+        <v>63.60786014428628</v>
+      </c>
+      <c r="G28">
         <v>19.64274202528233</v>
-      </c>
-      <c r="F28">
-        <v>63.60786014428626</v>
-      </c>
-      <c r="G28">
-        <v>16.74939783043139</v>
       </c>
     </row>
     <row r="29">
@@ -1073,22 +1073,22 @@
         </is>
       </c>
       <c r="B29">
+        <v>30.90058009911347</v>
+      </c>
+      <c r="C29">
         <v>28.43542302856116</v>
-      </c>
-      <c r="C29">
-        <v>30.90058009911347</v>
       </c>
       <c r="D29">
         <v>3.516740366392925</v>
       </c>
       <c r="E29">
-        <v>17.84620077721925</v>
+        <v>19.39334456278101</v>
       </c>
       <c r="F29">
         <v>62.76045465999973</v>
       </c>
       <c r="G29">
-        <v>19.39334456278101</v>
+        <v>17.84620077721925</v>
       </c>
     </row>
     <row r="30">
@@ -1098,22 +1098,22 @@
         </is>
       </c>
       <c r="B30">
+        <v>25.46143807097135</v>
+      </c>
+      <c r="C30">
         <v>36.41787334534833</v>
-      </c>
-      <c r="C30">
-        <v>25.46143807097135</v>
       </c>
       <c r="D30">
         <v>2.745904436860068</v>
       </c>
       <c r="E30">
-        <v>22.49692874692875</v>
+        <v>15.72865479115479</v>
       </c>
       <c r="F30">
         <v>61.77441646191646</v>
       </c>
       <c r="G30">
-        <v>15.72865479115479</v>
+        <v>22.49692874692875</v>
       </c>
     </row>
     <row r="31">
@@ -1123,22 +1123,22 @@
         </is>
       </c>
       <c r="B31">
+        <v>23.30237806835005</v>
+      </c>
+      <c r="C31">
         <v>26.00345787909847</v>
-      </c>
-      <c r="C31">
-        <v>23.30237806835005</v>
       </c>
       <c r="D31">
         <v>3.845642393597962</v>
       </c>
       <c r="E31">
-        <v>17.41623675597715</v>
+        <v>15.60714483829811</v>
       </c>
       <c r="F31">
         <v>66.97661840572475</v>
       </c>
       <c r="G31">
-        <v>15.60714483829811</v>
+        <v>17.41623675597715</v>
       </c>
     </row>
     <row r="32">
@@ -1148,22 +1148,22 @@
         </is>
       </c>
       <c r="B32">
+        <v>26.5037459864431</v>
+      </c>
+      <c r="C32">
         <v>33.85836603638958</v>
-      </c>
-      <c r="C32">
-        <v>26.5037459864431</v>
       </c>
       <c r="D32">
         <v>2.953479795585059</v>
       </c>
       <c r="E32">
-        <v>21.11369425688828</v>
+        <v>16.52743634523187</v>
       </c>
       <c r="F32">
-        <v>62.35886939787984</v>
+        <v>62.35886939787985</v>
       </c>
       <c r="G32">
-        <v>16.52743634523187</v>
+        <v>21.11369425688829</v>
       </c>
     </row>
     <row r="33">
@@ -1173,22 +1173,22 @@
         </is>
       </c>
       <c r="B33">
+        <v>23.55345194647202</v>
+      </c>
+      <c r="C33">
         <v>40.46722931873479</v>
-      </c>
-      <c r="C33">
-        <v>23.55345194647202</v>
       </c>
       <c r="D33">
         <v>2.471135328103716</v>
       </c>
       <c r="E33">
-        <v>24.67202855553495</v>
+        <v>14.36005006489894</v>
       </c>
       <c r="F33">
         <v>60.96792137956611</v>
       </c>
       <c r="G33">
-        <v>14.36005006489894</v>
+        <v>24.67202855553495</v>
       </c>
     </row>
     <row r="34">
@@ -1198,22 +1198,22 @@
         </is>
       </c>
       <c r="B34">
+        <v>28.75631512580802</v>
+      </c>
+      <c r="C34">
         <v>27.56293148208688</v>
-      </c>
-      <c r="C34">
-        <v>28.75631512580802</v>
       </c>
       <c r="D34">
         <v>3.628061117700412</v>
       </c>
       <c r="E34">
-        <v>17.63246182424654</v>
+        <v>18.39588902186769</v>
       </c>
       <c r="F34">
         <v>63.97164915388576</v>
       </c>
       <c r="G34">
-        <v>18.39588902186769</v>
+        <v>17.63246182424654</v>
       </c>
     </row>
     <row r="35">
@@ -1223,22 +1223,22 @@
         </is>
       </c>
       <c r="B35">
+        <v>24.71608416233823</v>
+      </c>
+      <c r="C35">
         <v>28.29474425565631</v>
-      </c>
-      <c r="C35">
-        <v>24.71608416233823</v>
       </c>
       <c r="D35">
         <v>3.534225264467953</v>
       </c>
       <c r="E35">
-        <v>18.49198814763672</v>
+        <v>16.15316015074365</v>
       </c>
       <c r="F35">
         <v>65.35485170161964</v>
       </c>
       <c r="G35">
-        <v>16.15316015074365</v>
+        <v>18.49198814763672</v>
       </c>
     </row>
     <row r="36">
@@ -1248,22 +1248,22 @@
         </is>
       </c>
       <c r="B36">
+        <v>26.78512122218532</v>
+      </c>
+      <c r="C36">
         <v>33.55197608767851</v>
-      </c>
-      <c r="C36">
-        <v>26.78512122218532</v>
       </c>
       <c r="D36">
         <v>2.980450383568424</v>
       </c>
       <c r="E36">
-        <v>20.92589715706075</v>
+        <v>16.70550463466418</v>
       </c>
       <c r="F36">
-        <v>62.36859820827508</v>
+        <v>62.36859820827507</v>
       </c>
       <c r="G36">
-        <v>16.70550463466418</v>
+        <v>20.92589715706074</v>
       </c>
     </row>
     <row r="37">
@@ -1273,22 +1273,22 @@
         </is>
       </c>
       <c r="B37">
+        <v>35.70973114442065</v>
+      </c>
+      <c r="C37">
         <v>18.08041874851297</v>
-      </c>
-      <c r="C37">
-        <v>35.70973114442065</v>
       </c>
       <c r="D37">
         <v>5.530845352142331</v>
       </c>
       <c r="E37">
-        <v>11.75655187351094</v>
+        <v>23.21977783966088</v>
       </c>
       <c r="F37">
         <v>65.02367028682818</v>
       </c>
       <c r="G37">
-        <v>23.21977783966088</v>
+        <v>11.75655187351094</v>
       </c>
     </row>
     <row r="38">
@@ -1298,22 +1298,22 @@
         </is>
       </c>
       <c r="B38">
+        <v>36.29403913470498</v>
+      </c>
+      <c r="C38">
         <v>16.54914503009393</v>
-      </c>
-      <c r="C38">
-        <v>36.29403913470498</v>
       </c>
       <c r="D38">
         <v>6.042608232519211</v>
       </c>
       <c r="E38">
-        <v>10.82753223215389</v>
+        <v>23.7459323639659</v>
       </c>
       <c r="F38">
         <v>65.42653540388021</v>
       </c>
       <c r="G38">
-        <v>23.7459323639659</v>
+        <v>10.82753223215389</v>
       </c>
     </row>
     <row r="39">
@@ -1323,22 +1323,22 @@
         </is>
       </c>
       <c r="B39">
+        <v>34.190598656951</v>
+      </c>
+      <c r="C39">
         <v>17.84540648664095</v>
-      </c>
-      <c r="C39">
-        <v>34.190598656951</v>
       </c>
       <c r="D39">
         <v>5.603682946357086</v>
       </c>
       <c r="E39">
-        <v>11.7376186448642</v>
+        <v>22.48848792406729</v>
       </c>
       <c r="F39">
         <v>65.7738934310685</v>
       </c>
       <c r="G39">
-        <v>22.48848792406729</v>
+        <v>11.7376186448642</v>
       </c>
     </row>
     <row r="40">
@@ -1348,22 +1348,22 @@
         </is>
       </c>
       <c r="B40">
+        <v>31.35660411880705</v>
+      </c>
+      <c r="C40">
         <v>26.15523795970644</v>
-      </c>
-      <c r="C40">
-        <v>31.35660411880705</v>
       </c>
       <c r="D40">
         <v>3.823325949244103</v>
       </c>
       <c r="E40">
-        <v>16.60525177952593</v>
+        <v>19.90745819808076</v>
       </c>
       <c r="F40">
         <v>63.4872900223933</v>
       </c>
       <c r="G40">
-        <v>19.90745819808076</v>
+        <v>16.60525177952593</v>
       </c>
     </row>
     <row r="41">
@@ -1373,22 +1373,22 @@
         </is>
       </c>
       <c r="B41">
+        <v>32.39788088661142</v>
+      </c>
+      <c r="C41">
         <v>23.39431789369737</v>
-      </c>
-      <c r="C41">
-        <v>32.39788088661142</v>
       </c>
       <c r="D41">
         <v>4.274542239461526</v>
       </c>
       <c r="E41">
+        <v>20.79557329587309</v>
+      </c>
+      <c r="F41">
+        <v>64.18806640056191</v>
+      </c>
+      <c r="G41">
         <v>15.016360303565</v>
-      </c>
-      <c r="F41">
-        <v>64.18806640056189</v>
-      </c>
-      <c r="G41">
-        <v>20.79557329587309</v>
       </c>
     </row>
     <row r="42">
@@ -1398,22 +1398,22 @@
         </is>
       </c>
       <c r="B42">
+        <v>20.19871466309191</v>
+      </c>
+      <c r="C42">
         <v>25.8802192169696</v>
-      </c>
-      <c r="C42">
-        <v>20.19871466309191</v>
       </c>
       <c r="D42">
         <v>3.863954905545399</v>
       </c>
       <c r="E42">
+        <v>13.82726045883941</v>
+      </c>
+      <c r="F42">
+        <v>68.45614035087719</v>
+      </c>
+      <c r="G42">
         <v>17.7165991902834</v>
-      </c>
-      <c r="F42">
-        <v>68.45614035087718</v>
-      </c>
-      <c r="G42">
-        <v>13.8272604588394</v>
       </c>
     </row>
     <row r="43">
@@ -1423,22 +1423,22 @@
         </is>
       </c>
       <c r="B43">
+        <v>30.65324633991089</v>
+      </c>
+      <c r="C43">
         <v>27.71323997453851</v>
-      </c>
-      <c r="C43">
-        <v>30.65324633991089</v>
       </c>
       <c r="D43">
         <v>3.608383577375825</v>
       </c>
       <c r="E43">
-        <v>17.49943477277866</v>
+        <v>19.35589217976738</v>
       </c>
       <c r="F43">
         <v>63.14467304745397</v>
       </c>
       <c r="G43">
-        <v>19.35589217976738</v>
+        <v>17.49943477277866</v>
       </c>
     </row>
     <row r="44">
@@ -1448,22 +1448,22 @@
         </is>
       </c>
       <c r="B44">
+        <v>30.40486333178906</v>
+      </c>
+      <c r="C44">
         <v>31.02972914948192</v>
-      </c>
-      <c r="C44">
-        <v>30.40486333178906</v>
       </c>
       <c r="D44">
         <v>3.222715851571319</v>
       </c>
       <c r="E44">
-        <v>19.22123918582188</v>
+        <v>18.83416860318616</v>
       </c>
       <c r="F44">
         <v>61.94459221099197</v>
       </c>
       <c r="G44">
-        <v>18.83416860318616</v>
+        <v>19.22123918582188</v>
       </c>
     </row>
     <row r="45">
@@ -1473,22 +1473,22 @@
         </is>
       </c>
       <c r="B45">
+        <v>33.98407884761183</v>
+      </c>
+      <c r="C45">
         <v>30.02274450341168</v>
-      </c>
-      <c r="C45">
-        <v>33.98407884761183</v>
       </c>
       <c r="D45">
         <v>3.330808080808081</v>
       </c>
       <c r="E45">
-        <v>18.30578989945684</v>
+        <v>20.72113717785739</v>
       </c>
       <c r="F45">
         <v>60.97307292268577</v>
       </c>
       <c r="G45">
-        <v>20.72113717785739</v>
+        <v>18.30578989945684</v>
       </c>
     </row>
     <row r="46">
@@ -1498,22 +1498,22 @@
         </is>
       </c>
       <c r="B46">
+        <v>30.6117136659436</v>
+      </c>
+      <c r="C46">
         <v>32.8763557483731</v>
-      </c>
-      <c r="C46">
-        <v>30.6117136659436</v>
       </c>
       <c r="D46">
         <v>3.041699656901557</v>
       </c>
       <c r="E46">
-        <v>20.1093302197219</v>
+        <v>18.72412695042989</v>
       </c>
       <c r="F46">
         <v>61.16654282984821</v>
       </c>
       <c r="G46">
-        <v>18.72412695042989</v>
+        <v>20.1093302197219</v>
       </c>
     </row>
     <row r="47">
@@ -1523,22 +1523,22 @@
         </is>
       </c>
       <c r="B47">
+        <v>31.6083773891826</v>
+      </c>
+      <c r="C47">
         <v>34.15006100040667</v>
-      </c>
-      <c r="C47">
-        <v>31.6083773891826</v>
       </c>
       <c r="D47">
         <v>2.928252456088122</v>
       </c>
       <c r="E47">
-        <v>20.60230618253189</v>
+        <v>19.0689401373896</v>
       </c>
       <c r="F47">
         <v>60.3287536800785</v>
       </c>
       <c r="G47">
-        <v>19.0689401373896</v>
+        <v>20.60230618253189</v>
       </c>
     </row>
     <row r="48">
@@ -1548,22 +1548,22 @@
         </is>
       </c>
       <c r="B48">
+        <v>34.18571200255714</v>
+      </c>
+      <c r="C48">
         <v>38.91641361674924</v>
-      </c>
-      <c r="C48">
-        <v>34.18571200255714</v>
       </c>
       <c r="D48">
         <v>2.569609856262834</v>
       </c>
       <c r="E48">
-        <v>22.48176530329609</v>
+        <v>19.74886898716647</v>
       </c>
       <c r="F48">
         <v>57.76936570953744</v>
       </c>
       <c r="G48">
-        <v>19.74886898716647</v>
+        <v>22.48176530329609</v>
       </c>
     </row>
     <row r="49">
@@ -1573,22 +1573,22 @@
         </is>
       </c>
       <c r="B49">
+        <v>29.56472923391543</v>
+      </c>
+      <c r="C49">
         <v>29.23592036409568</v>
-      </c>
-      <c r="C49">
-        <v>29.56472923391543</v>
       </c>
       <c r="D49">
         <v>3.420449869702373</v>
       </c>
       <c r="E49">
-        <v>18.41045388548703</v>
+        <v>18.61751152073733</v>
       </c>
       <c r="F49">
         <v>62.97203459377564</v>
       </c>
       <c r="G49">
-        <v>18.61751152073733</v>
+        <v>18.41045388548703</v>
       </c>
     </row>
     <row r="50">
@@ -1598,22 +1598,22 @@
         </is>
       </c>
       <c r="B50">
+        <v>31.54389183583935</v>
+      </c>
+      <c r="C50">
         <v>28.81585769552905</v>
-      </c>
-      <c r="C50">
-        <v>31.54389183583935</v>
       </c>
       <c r="D50">
         <v>3.470311418685121</v>
       </c>
       <c r="E50">
-        <v>17.96950779714975</v>
+        <v>19.67070410625016</v>
       </c>
       <c r="F50">
         <v>62.35978809660009</v>
       </c>
       <c r="G50">
-        <v>19.67070410625016</v>
+        <v>17.96950779714975</v>
       </c>
     </row>
     <row r="51">
@@ -1623,22 +1623,22 @@
         </is>
       </c>
       <c r="B51">
+        <v>29.45489321007332</v>
+      </c>
+      <c r="C51">
         <v>28.85718839655722</v>
-      </c>
-      <c r="C51">
-        <v>29.45489321007332</v>
       </c>
       <c r="D51">
         <v>3.465341066003866</v>
       </c>
       <c r="E51">
-        <v>18.22803926503902</v>
+        <v>18.60558771709036</v>
       </c>
       <c r="F51">
-        <v>63.16637301787063</v>
+        <v>63.16637301787062</v>
       </c>
       <c r="G51">
-        <v>18.60558771709036</v>
+        <v>18.22803926503901</v>
       </c>
     </row>
     <row r="52">
@@ -1648,22 +1648,22 @@
         </is>
       </c>
       <c r="B52">
+        <v>31.2207348112456</v>
+      </c>
+      <c r="C52">
         <v>22.52618080786493</v>
-      </c>
-      <c r="C52">
-        <v>31.2207348112456</v>
       </c>
       <c r="D52">
         <v>4.439278937381404</v>
       </c>
       <c r="E52">
-        <v>14.65146843249255</v>
+        <v>20.30657635343477</v>
       </c>
       <c r="F52">
         <v>65.04195521407269</v>
       </c>
       <c r="G52">
-        <v>20.30657635343477</v>
+        <v>14.65146843249255</v>
       </c>
     </row>
     <row r="53">
@@ -1673,22 +1673,22 @@
         </is>
       </c>
       <c r="B53">
+        <v>29.21413869665981</v>
+      </c>
+      <c r="C53">
         <v>27.79281396366465</v>
-      </c>
-      <c r="C53">
-        <v>29.21413869665981</v>
       </c>
       <c r="D53">
         <v>3.598052364569363</v>
       </c>
       <c r="E53">
-        <v>17.7016453684015</v>
+        <v>18.6069076570532</v>
       </c>
       <c r="F53">
         <v>63.69144697454531</v>
       </c>
       <c r="G53">
-        <v>18.6069076570532</v>
+        <v>17.7016453684015</v>
       </c>
     </row>
   </sheetData>
